--- a/table/Supplementary Table 10.xlsx
+++ b/table/Supplementary Table 10.xlsx
@@ -343,28 +343,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Series</t>
+          <t>Forecast horizon (years)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Model role</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Rolling origins</t>
+          <t>Rolling origins per series</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -374,1244 +374,786 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>MAE</t>
+          <t>MAPE (%)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>RMSE</t>
+          <t>MASE</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>MAPE (%)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>MASE</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Empirical coverage of the nominal 95% range (%)</t>
+          <t>Empirical coverage of nominal 95% construction (%)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>h = 1 year ahead</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VLW</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ARIMA</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="D2">
         <v>14</v>
       </c>
       <c r="E2">
-        <v>69</v>
+        <v>112</v>
       </c>
       <c r="F2">
-        <v>10.9502292920655</v>
+        <v>1.43</v>
       </c>
       <c r="G2">
-        <v>14.33235021104475</v>
+        <v>0.716</v>
       </c>
       <c r="H2">
-        <v>4.154823410529678</v>
-      </c>
-      <c r="I2">
-        <v>2.513778843485355</v>
-      </c>
-      <c r="J2">
-        <v>43.47826086956522</v>
+        <v>58.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>h = 1 year ahead</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VLW</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Drift</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="D3">
         <v>14</v>
       </c>
       <c r="E3">
-        <v>69</v>
+        <v>112</v>
       </c>
       <c r="F3">
-        <v>10.63987759295653</v>
+        <v>1.68</v>
       </c>
       <c r="G3">
-        <v>13.82273577584054</v>
+        <v>0.859</v>
       </c>
       <c r="H3">
-        <v>4.019833426394761</v>
-      </c>
-      <c r="I3">
-        <v>2.451082947251843</v>
-      </c>
-      <c r="J3">
-        <v>39.1304347826087</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>h = 1 year ahead</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VLW</t>
+          <t>Drift</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="D4">
         <v>14</v>
       </c>
       <c r="E4">
-        <v>69</v>
+        <v>112</v>
       </c>
       <c r="F4">
-        <v>12.11079946114768</v>
+        <v>2.54</v>
       </c>
       <c r="G4">
-        <v>16.24449580918776</v>
+        <v>1.25</v>
       </c>
       <c r="H4">
-        <v>4.650710835596287</v>
-      </c>
-      <c r="I4">
-        <v>2.802746681845645</v>
-      </c>
-      <c r="J4">
-        <v>52.17391304347826</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>h = 1 year ahead</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VLW</t>
+          <t>Naive</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Naive</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="D5">
         <v>14</v>
       </c>
       <c r="E5">
-        <v>69</v>
+        <v>112</v>
       </c>
       <c r="F5">
-        <v>23.57778271868277</v>
+        <v>4.19</v>
       </c>
       <c r="G5">
-        <v>27.88218795800499</v>
+        <v>2.028</v>
       </c>
       <c r="H5">
-        <v>9.148642361169934</v>
-      </c>
-      <c r="I5">
-        <v>5.487901438929018</v>
-      </c>
-      <c r="J5">
-        <v>36.23188405797102</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Low income</t>
+          <t>h = 2 years ahead</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DALY</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARIMA</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E6">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="F6">
-        <v>4728.712531892266</v>
+        <v>3.2</v>
       </c>
       <c r="G6">
-        <v>6811.720958229244</v>
+        <v>1.709</v>
       </c>
       <c r="H6">
-        <v>4.236084851669204</v>
-      </c>
-      <c r="I6">
-        <v>2.565690293850184</v>
-      </c>
-      <c r="J6">
-        <v>69.56521739130434</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Low income</t>
+          <t>h = 2 years ahead</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DALY</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Drift</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="D7">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E7">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="F7">
-        <v>12725.34816901934</v>
+        <v>3.13</v>
       </c>
       <c r="G7">
-        <v>15589.33626332987</v>
+        <v>1.682</v>
       </c>
       <c r="H7">
-        <v>11.86681736057764</v>
-      </c>
-      <c r="I7">
-        <v>7.016938868474196</v>
-      </c>
-      <c r="J7">
-        <v>4.347826086956522</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Low income</t>
+          <t>h = 2 years ahead</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DALY</t>
+          <t>Drift</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="D8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E8">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="F8">
-        <v>5468.902781195698</v>
+        <v>4.79</v>
       </c>
       <c r="G8">
-        <v>7655.11337596306</v>
+        <v>2.475</v>
       </c>
       <c r="H8">
-        <v>4.932336441461872</v>
-      </c>
-      <c r="I8">
-        <v>2.982226585939642</v>
-      </c>
-      <c r="J8">
-        <v>60.86956521739131</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Low income</t>
+          <t>h = 2 years ahead</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DALY</t>
+          <t>Naive</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Naive</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="D9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E9">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="F9">
-        <v>18230.93082420695</v>
+        <v>8.23</v>
       </c>
       <c r="G9">
-        <v>21652.80989319392</v>
+        <v>4.188</v>
       </c>
       <c r="H9">
-        <v>17.2833233112116</v>
-      </c>
-      <c r="I9">
-        <v>10.18156696114595</v>
-      </c>
-      <c r="J9">
-        <v>4.347826086956522</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Low income</t>
+          <t>h = 3 years ahead</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VLW</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ARIMA</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="D10">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E10">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="F10">
-        <v>0.06371295436689461</v>
+        <v>4.27</v>
       </c>
       <c r="G10">
-        <v>0.09259625993065763</v>
+        <v>2.378</v>
       </c>
       <c r="H10">
-        <v>4.171995799440772</v>
-      </c>
-      <c r="I10">
-        <v>2.453334518655518</v>
-      </c>
-      <c r="J10">
-        <v>78.26086956521739</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Low income</t>
+          <t>h = 3 years ahead</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VLW</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Drift</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="D11">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E11">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="F11">
-        <v>0.1693532438708267</v>
+        <v>5.04</v>
       </c>
       <c r="G11">
-        <v>0.2079163019000961</v>
+        <v>2.805</v>
       </c>
       <c r="H11">
-        <v>11.52536744494665</v>
-      </c>
-      <c r="I11">
-        <v>6.615229629085206</v>
-      </c>
-      <c r="J11">
-        <v>5.797101449275362</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Low income</t>
+          <t>h = 3 years ahead</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VLW</t>
+          <t>Drift</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="D12">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E12">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="F12">
-        <v>0.08682789541846367</v>
+        <v>6.84</v>
       </c>
       <c r="G12">
-        <v>0.1257312146781065</v>
+        <v>3.678</v>
       </c>
       <c r="H12">
-        <v>5.676888282132383</v>
-      </c>
-      <c r="I12">
-        <v>3.332960364110004</v>
-      </c>
-      <c r="J12">
-        <v>50.72463768115942</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Low income</t>
+          <t>h = 3 years ahead</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VLW</t>
+          <t>Naive</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Naive</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="D13">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E13">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="F13">
-        <v>0.246205345331045</v>
+        <v>12.1</v>
       </c>
       <c r="G13">
-        <v>0.292293209818367</v>
+        <v>6.426</v>
       </c>
       <c r="H13">
-        <v>17.05740640707186</v>
-      </c>
-      <c r="I13">
-        <v>9.745117096071326</v>
-      </c>
-      <c r="J13">
-        <v>4.347826086956522</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Lower middle income</t>
+          <t>h = 4 years ahead</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DALY</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ARIMA</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="D14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E14">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F14">
-        <v>49426.43609114087</v>
+        <v>5.11</v>
       </c>
       <c r="G14">
-        <v>69709.48851421612</v>
+        <v>2.899</v>
       </c>
       <c r="H14">
-        <v>4.189659760031997</v>
-      </c>
-      <c r="I14">
-        <v>2.047986567518579</v>
-      </c>
-      <c r="J14">
-        <v>66.66666666666666</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Lower middle income</t>
+          <t>h = 4 years ahead</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DALY</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Drift</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="D15">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E15">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F15">
-        <v>101394.2555079829</v>
+        <v>6.28</v>
       </c>
       <c r="G15">
-        <v>126152.6532593337</v>
+        <v>3.568</v>
       </c>
       <c r="H15">
-        <v>8.633029768854529</v>
-      </c>
-      <c r="I15">
-        <v>4.261724816585298</v>
-      </c>
-      <c r="J15">
-        <v>15.94202898550724</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lower middle income</t>
+          <t>h = 4 years ahead</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DALY</t>
+          <t>Drift</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="D16">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E16">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F16">
-        <v>52520.29387166261</v>
+        <v>8.5</v>
       </c>
       <c r="G16">
-        <v>70120.05267100989</v>
+        <v>4.714</v>
       </c>
       <c r="H16">
-        <v>4.494409787145069</v>
-      </c>
-      <c r="I16">
-        <v>2.213826009531883</v>
-      </c>
-      <c r="J16">
-        <v>60.86956521739131</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Lower middle income</t>
+          <t>h = 4 years ahead</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DALY</t>
+          <t>Naive</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Naive</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="D17">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E17">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F17">
-        <v>176155.4968705308</v>
+        <v>15.56</v>
       </c>
       <c r="G17">
-        <v>207151.8120318164</v>
+        <v>8.548</v>
       </c>
       <c r="H17">
-        <v>15.42269152486982</v>
-      </c>
-      <c r="I17">
-        <v>7.5081016281795</v>
-      </c>
-      <c r="J17">
-        <v>14.49275362318841</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Lower middle income</t>
+          <t>h = 5 years ahead</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>VLW</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ARIMA</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="D18">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E18">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="F18">
-        <v>2.834420853998448</v>
+        <v>5.68</v>
       </c>
       <c r="G18">
-        <v>3.965535114876063</v>
+        <v>3.306</v>
       </c>
       <c r="H18">
-        <v>3.976881658530389</v>
-      </c>
-      <c r="I18">
-        <v>1.893511414605288</v>
-      </c>
-      <c r="J18">
-        <v>69.56521739130434</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Lower middle income</t>
+          <t>h = 5 years ahead</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>VLW</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Drift</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="D19">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E19">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="F19">
-        <v>5.87294752850426</v>
+        <v>7.04</v>
       </c>
       <c r="G19">
-        <v>7.293709670095278</v>
+        <v>4.077</v>
       </c>
       <c r="H19">
-        <v>8.293889902150994</v>
-      </c>
-      <c r="I19">
-        <v>3.964860394558976</v>
-      </c>
-      <c r="J19">
-        <v>17.39130434782609</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Lower middle income</t>
+          <t>h = 5 years ahead</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>VLW</t>
+          <t>Drift</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="D20">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E20">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="F20">
-        <v>3.205590997197211</v>
+        <v>10.33</v>
       </c>
       <c r="G20">
-        <v>4.297115589551401</v>
+        <v>5.946</v>
       </c>
       <c r="H20">
-        <v>4.529396474826786</v>
-      </c>
-      <c r="I20">
-        <v>2.174677123529417</v>
-      </c>
-      <c r="J20">
-        <v>59.42028985507246</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Lower middle income</t>
+          <t>h = 5 years ahead</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>VLW</t>
+          <t>Naive</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Naive</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="D21">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E21">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="F21">
-        <v>10.52332075202026</v>
+        <v>19.04</v>
       </c>
       <c r="G21">
-        <v>12.33254239037486</v>
+        <v>10.854</v>
       </c>
       <c r="H21">
-        <v>15.31580032692607</v>
-      </c>
-      <c r="I21">
-        <v>7.211237206153179</v>
-      </c>
-      <c r="J21">
-        <v>14.49275362318841</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>h = 6 years ahead</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>VLW</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ARIMA</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="D22">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E22">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F22">
-        <v>18.53810530430418</v>
+        <v>6.96</v>
       </c>
       <c r="G22">
-        <v>23.91061341500217</v>
+        <v>4.189</v>
       </c>
       <c r="H22">
-        <v>4.448241757782196</v>
-      </c>
-      <c r="I22">
-        <v>2.537724424626481</v>
-      </c>
-      <c r="J22">
-        <v>33.33333333333333</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>h = 6 years ahead</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>VLW</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Drift</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="D23">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E23">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F23">
-        <v>18.5194542520648</v>
+        <v>8.34</v>
       </c>
       <c r="G23">
-        <v>24.01922479764807</v>
+        <v>4.983</v>
       </c>
       <c r="H23">
-        <v>4.392478174646231</v>
-      </c>
-      <c r="I23">
-        <v>2.538051068558584</v>
-      </c>
-      <c r="J23">
-        <v>40.57971014492754</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>h = 6 years ahead</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>VLW</t>
+          <t>Drift</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="D24">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E24">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F24">
-        <v>21.48215951458487</v>
+        <v>12.35</v>
       </c>
       <c r="G24">
-        <v>27.79654461853012</v>
+        <v>7.441</v>
       </c>
       <c r="H24">
-        <v>5.180782146476312</v>
-      </c>
-      <c r="I24">
-        <v>2.94313009126682</v>
-      </c>
-      <c r="J24">
-        <v>52.17391304347826</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>h = 6 years ahead</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>VLW</t>
+          <t>Naive</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Naive</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="D25">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E25">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F25">
-        <v>39.56466523072831</v>
+        <v>22.5</v>
       </c>
       <c r="G25">
-        <v>47.23651091306396</v>
+        <v>13.391</v>
       </c>
       <c r="H25">
-        <v>9.622758965118267</v>
-      </c>
-      <c r="I25">
-        <v>5.473317360036434</v>
-      </c>
-      <c r="J25">
-        <v>34.78260869565217</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Upper middle income</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>DALY</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>ARIMA</t>
-        </is>
-      </c>
-      <c r="D26">
-        <v>14</v>
-      </c>
-      <c r="E26">
-        <v>69</v>
-      </c>
-      <c r="F26">
-        <v>179014.307000543</v>
-      </c>
-      <c r="G26">
-        <v>229640.8912151678</v>
-      </c>
-      <c r="H26">
-        <v>4.10718713917293</v>
-      </c>
-      <c r="I26">
-        <v>2.433929380334716</v>
-      </c>
-      <c r="J26">
-        <v>40.57971014492754</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Upper middle income</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>DALY</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Drift</t>
-        </is>
-      </c>
-      <c r="D27">
-        <v>14</v>
-      </c>
-      <c r="E27">
-        <v>69</v>
-      </c>
-      <c r="F27">
-        <v>168843.3375736893</v>
-      </c>
-      <c r="G27">
-        <v>217071.5880243705</v>
-      </c>
-      <c r="H27">
-        <v>3.876429794817598</v>
-      </c>
-      <c r="I27">
-        <v>2.305066947645936</v>
-      </c>
-      <c r="J27">
-        <v>43.47826086956522</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Upper middle income</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>DALY</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>ETS</t>
-        </is>
-      </c>
-      <c r="D28">
-        <v>14</v>
-      </c>
-      <c r="E28">
-        <v>69</v>
-      </c>
-      <c r="F28">
-        <v>214479.5659552971</v>
-      </c>
-      <c r="G28">
-        <v>280704.5161124098</v>
-      </c>
-      <c r="H28">
-        <v>4.967917704575404</v>
-      </c>
-      <c r="I28">
-        <v>2.922356768442076</v>
-      </c>
-      <c r="J28">
-        <v>52.17391304347826</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Upper middle income</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>DALY</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Naive</t>
-        </is>
-      </c>
-      <c r="D29">
-        <v>14</v>
-      </c>
-      <c r="E29">
-        <v>69</v>
-      </c>
-      <c r="F29">
-        <v>376167.270759218</v>
-      </c>
-      <c r="G29">
-        <v>449001.8872011568</v>
-      </c>
-      <c r="H29">
-        <v>8.842480813590777</v>
-      </c>
-      <c r="I29">
-        <v>5.182835218379067</v>
-      </c>
-      <c r="J29">
-        <v>37.68115942028986</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Upper middle income</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>VLW</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>ARIMA</t>
-        </is>
-      </c>
-      <c r="D30">
-        <v>14</v>
-      </c>
-      <c r="E30">
-        <v>69</v>
-      </c>
-      <c r="F30">
-        <v>25.33897340306774</v>
-      </c>
-      <c r="G30">
-        <v>32.26035634419024</v>
-      </c>
-      <c r="H30">
-        <v>4.159035395787717</v>
-      </c>
-      <c r="I30">
-        <v>2.501959471856946</v>
-      </c>
-      <c r="J30">
-        <v>39.1304347826087</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Upper middle income</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>VLW</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Drift</t>
-        </is>
-      </c>
-      <c r="D31">
-        <v>14</v>
-      </c>
-      <c r="E31">
-        <v>69</v>
-      </c>
-      <c r="F31">
-        <v>24.21209750467598</v>
-      </c>
-      <c r="G31">
-        <v>30.95181217794559</v>
-      </c>
-      <c r="H31">
-        <v>3.963591074304833</v>
-      </c>
-      <c r="I31">
-        <v>2.393591431987648</v>
-      </c>
-      <c r="J31">
-        <v>43.47826086956522</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Upper middle income</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>VLW</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>ETS</t>
-        </is>
-      </c>
-      <c r="D32">
-        <v>14</v>
-      </c>
-      <c r="E32">
-        <v>69</v>
-      </c>
-      <c r="F32">
-        <v>29.85827338869964</v>
-      </c>
-      <c r="G32">
-        <v>39.43327508010787</v>
-      </c>
-      <c r="H32">
-        <v>4.900484201070729</v>
-      </c>
-      <c r="I32">
-        <v>2.93633737289659</v>
-      </c>
-      <c r="J32">
-        <v>55.07246376811595</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Upper middle income</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>VLW</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Naive</t>
-        </is>
-      </c>
-      <c r="D33">
-        <v>14</v>
-      </c>
-      <c r="E33">
-        <v>69</v>
-      </c>
-      <c r="F33">
-        <v>52.27961570327714</v>
-      </c>
-      <c r="G33">
-        <v>62.66502197406115</v>
-      </c>
-      <c r="H33">
-        <v>8.736220350264343</v>
-      </c>
-      <c r="I33">
-        <v>5.21418659578468</v>
-      </c>
-      <c r="J33">
-        <v>36.23188405797102</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
